--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
   <si>
     <t xml:space="preserve">TABLEAU 1 - Moyenne journaliere de ventes de SOJA en juillet (tonnes/jour) par agence/region</t>
   </si>
   <si>
-    <t xml:space="preserve">Periode: 01/07 au 21/07 (18 jours avec ventes). Etat: Livree + Validee.</t>
+    <t xml:space="preserve">Periode: 01/07 au 21/07. Etat: Livree uniquement.</t>
   </si>
   <si>
     <t xml:space="preserve">Agence</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">TABLEAU 2 - Commandes contenant du SOJA le 21 juillet 2026 par agence</t>
   </si>
   <si>
-    <t xml:space="preserve">Tous etats confondus. Ratio en sacs (soja:conc).</t>
+    <t xml:space="preserve">Etat: Livree uniquement. Ratio en sacs (soja:conc).</t>
   </si>
   <si>
     <t xml:space="preserve">Cmds soja</t>
@@ -123,42 +123,42 @@
     <t xml:space="preserve">Ratio moy (sacs)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7:1</t>
+    <t xml:space="preserve">2.8:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3:1</t>
   </si>
   <si>
     <t xml:space="preserve">2.9:1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3:1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Distribution des ratios (bundle uniquement)</t>
   </si>
   <si>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">10:1 a 20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">3%</t>
+    <t xml:space="preserve">4%</t>
   </si>
   <si>
     <t xml:space="preserve">&gt; 20:1</t>
@@ -195,6 +195,9 @@
     <t xml:space="preserve">TABLEAU 3 - Commandes contenant du SOJA sans concentres le 21 juillet 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Etat: Livree uniquement.</t>
+  </si>
+  <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
@@ -228,48 +231,12 @@
     <t xml:space="preserve">FERME MODERNE DU SUD</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-125003</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DJIOMETSA TETSOPMO GEORGE BALBAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En cours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125110</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KAM APPOLINAIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125088</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DJUIKOM MARLISE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125090</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COGESDI SARL</t>
-  </si>
-  <si>
     <t xml:space="preserve">SO2607-125024</t>
   </si>
   <si>
     <t xml:space="preserve"> MME NGOBOU SOREL</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-125085</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VETOCAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">SO2607-124997</t>
   </si>
   <si>
@@ -288,18 +255,6 @@
     <t xml:space="preserve"> PROVOCAM</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-124925</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ABOUBAKAR NGNAZOKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAKONDJOU HONORE</t>
-  </si>
-  <si>
     <t xml:space="preserve">SO2607-125065</t>
   </si>
   <si>
@@ -352,12 +307,6 @@
   </si>
   <si>
     <t xml:space="preserve"> CLIENTS COMPTOIR MESSASSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124987</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR </t>
   </si>
   <si>
     <t xml:space="preserve">SO2607-124976</t>
@@ -851,10 +800,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1390.8</v>
+        <v>1177.5</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>77.3</v>
+        <v>65.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -865,10 +814,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>810.8</v>
+        <v>685.2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>45</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -879,10 +828,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>410.1</v>
+        <v>408.3</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -893,10 +842,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>636.6</v>
+        <v>500</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>35.4</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -935,10 +884,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>214.1</v>
+        <v>203.1</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -963,10 +912,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>194.5</v>
+        <v>193.2</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -977,10 +926,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>114.8</v>
+        <v>111.2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1005,10 +954,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>262.1</v>
+        <v>260.1</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1033,10 +982,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>232.6</v>
+        <v>194.4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1047,10 +996,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2322.6</v>
+        <v>1972.7</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>129</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1061,10 +1010,10 @@
         <v>11</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1253.3</v>
+        <v>1233.8</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>69.6</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1075,10 +1024,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1432.5</v>
+        <v>1268.7</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>79.6</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1087,10 +1036,10 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="n">
-        <v>5008.5</v>
+        <v>4475.2</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>278.2</v>
+        <v>248.6</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1061,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -1163,10 +1112,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -1177,19 +1126,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>34</v>
@@ -1197,170 +1146,170 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>6</v>
@@ -1372,144 +1321,104 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="A17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8" t="n">
-        <v>149</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>35</v>
+      <c r="A19" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>45</v>
+      <c r="A21" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="0" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1532,7 +1441,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1556,67 +1465,46 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -1625,310 +1513,310 @@
         <v>11</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="H16" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>15</v>
@@ -1937,24 +1825,24 @@
         <v>11</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>15</v>
@@ -1963,108 +1851,108 @@
         <v>11</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="H18" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.1</v>
@@ -2073,232 +1961,50 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="n">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="8" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>1473</v>
-      </c>
-      <c r="H31" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="H24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -9,8 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="T2 - Commandes soja 21-07" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="T3 - Soja-only 21-07" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="T2 - Commandes soja 22-07" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="T3 - Soja-only 22-07" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
-  <si>
-    <t xml:space="preserve">TABLEAU 1 - Moyenne journaliere de ventes de SOJA en juillet (tonnes/jour) par agence/region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Periode: 01/07 au 21/07. Etat: Livree uniquement.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="128">
+  <si>
+    <t xml:space="preserve">TABLEAU 1 - Moyenne journaliere SOJA juillet par agence/region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/07 au 22/07 (19j). Livree. lun-sam.</t>
   </si>
   <si>
     <t xml:space="preserve">Agence</t>
@@ -36,10 +37,10 @@
     <t xml:space="preserve">Region</t>
   </si>
   <si>
-    <t xml:space="preserve">Total soja juillet (t)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moyenne/jour (t)</t>
+    <t xml:space="preserve">Total soja (t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moy/jour (t)</t>
   </si>
   <si>
     <t xml:space="preserve">Famla</t>
@@ -105,61 +106,58 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">TABLEAU 2 - Commandes contenant du SOJA le 21 juillet 2026 par agence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etat: Livree uniquement. Ratio en sacs (soja:conc).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmds soja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmds soja+conc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmds soja-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio moy (sacs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1:1</t>
+    <t xml:space="preserve">TABLEAU 2 - Commandes SOJA le 22/07 par agence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livree. Ratio en sacs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soja-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio moy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6:1</t>
   </si>
   <si>
     <t xml:space="preserve">2.1:1</t>
   </si>
   <si>
+    <t xml:space="preserve">1.9:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7:1</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.5:1</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5:1</t>
+    <t xml:space="preserve">1.0:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2:1</t>
   </si>
   <si>
     <t xml:space="preserve">2.4:1</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution des ratios (bundle uniquement)</t>
+    <t xml:space="preserve">2.6:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution ratios</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;= 3:1</t>
@@ -168,40 +166,37 @@
     <t xml:space="preserve">66%</t>
   </si>
   <si>
-    <t xml:space="preserve">3:1 a 5:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5:1 a 10:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:1 a 20:1</t>
+    <t xml:space="preserve">3-5:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-10:1</t>
   </si>
   <si>
     <t xml:space="preserve">4%</t>
   </si>
   <si>
+    <t xml:space="preserve">10-20:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
     <t xml:space="preserve">&gt; 20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABLEAU 3 - Commandes contenant du SOJA sans concentres le 21 juillet 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etat: Livree uniquement.</t>
+    <t xml:space="preserve">TABLEAU 3 - SOJA sans concentres le 22/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livree.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">N commande</t>
+    <t xml:space="preserve">N cmd</t>
   </si>
   <si>
     <t xml:space="preserve">Client</t>
@@ -210,109 +205,208 @@
     <t xml:space="preserve">Soja (t)</t>
   </si>
   <si>
-    <t xml:space="preserve">Soja (sacs)</t>
+    <t xml:space="preserve">Sacs</t>
   </si>
   <si>
     <t xml:space="preserve">Etat</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-124947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRADU-COOP CA</t>
+    <t xml:space="preserve">SO2607-125332</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DOUANGUIM CHARLIN</t>
   </si>
   <si>
     <t xml:space="preserve">Livrée</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-124954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERME MODERNE DU SUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MME NGOBOU SOREL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUPE ELEVAGE PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124885</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> YEMELONG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124902</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PROVOCAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125065</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KUETCHE FOGANG THOMAS TIERY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125075</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TCHONBEUA AUGUSTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124894</t>
+    <t xml:space="preserve">SO2607-125264</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SIGNE WILLIAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125144</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ROCHE KENGNE RAYMOND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125220</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABOUBAKAR NGNAZOKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125224</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FOTIE NGOMPE DANIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COOP AFAA'MBONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125286</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr TCHOFFO KAFO ERNEST ALBIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125331</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NZOUANKEU MANGA EPSE FOSSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125336</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PROVENDERIE LA GRACE DIVINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125306</t>
   </si>
   <si>
     <t xml:space="preserve"> CLIENTS COMPTOIR BERTOUA</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-125045</t>
+    <t xml:space="preserve">SO2607-125248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125253</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLIENTS COMPTOIR NGAOUNDERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125126</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLIENT COMPTOIR AXE LOURD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125150</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLIENT COMPTOIR NKONGSSAMBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125163</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLIENTS COMPTOIR FAMLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125185</t>
   </si>
   <si>
     <t xml:space="preserve"> CLIENTS COMPTOIR NKOABANG</t>
   </si>
   <si>
-    <t xml:space="preserve">SO2607-125042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124911</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLIENT COMPTOIR AXE LOURD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-125101</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLIENTS COMPTOIR MESSASSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO2607-124976</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CLIENT COMPTOIR NKONGSSAMBA</t>
+    <t xml:space="preserve">SO2607-125237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2607-125172</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLEAU 4 - Stock SOJA et date rupture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 000 sacs (8 000 t). Moy/jour sur juillet (19j, Livree).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacs/jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t/jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jours stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date rupture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceleration +20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ralentissement -20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parametres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160,000 sacs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 000 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventes juillet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92,815 sacs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4640.7 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moyenne/jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,885 sacs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">244.2 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jours ouvrables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6j/sem (lun-sam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/07/2026</t>
   </si>
 </sst>
 </file>
@@ -384,7 +478,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,7 +500,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
-        <bgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -459,7 +559,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,6 +601,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -550,11 +654,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFD966"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFD966"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -761,8 +865,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -800,10 +904,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1177.5</v>
+        <v>1213.6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>65.4</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -814,10 +918,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>685.2</v>
+        <v>733.7</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -831,7 +935,7 @@
         <v>408.3</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -842,10 +946,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>500</v>
+        <v>532.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -859,7 +963,7 @@
         <v>295.2</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>16.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -870,10 +974,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>169.7</v>
+        <v>175.7</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>9.4</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -884,10 +988,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>203.1</v>
+        <v>209.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -898,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>117.1</v>
+        <v>123.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>6.5</v>
@@ -912,10 +1016,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>193.2</v>
+        <v>193.3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -926,10 +1030,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>111.2</v>
+        <v>115.9</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -940,10 +1044,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>102.4</v>
+        <v>110.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -954,10 +1058,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>260.1</v>
+        <v>268</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -968,10 +1072,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>57.8</v>
+        <v>59.1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -982,10 +1086,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>194.4</v>
+        <v>202.4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -996,10 +1100,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1972.7</v>
+        <v>2041.1</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>109.6</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1010,10 +1114,10 @@
         <v>11</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1233.8</v>
+        <v>1254.1</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>68.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1024,10 +1128,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1268.7</v>
+        <v>1345.5</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1036,10 +1140,10 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="n">
-        <v>4475.2</v>
+        <v>4640.7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>248.6</v>
+        <v>244.2</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1170,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1112,13 +1216,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -1126,16 +1230,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>4</v>
@@ -1146,22 +1250,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1172,16 +1276,16 @@
         <v>9</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1192,16 +1296,16 @@
         <v>11</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1212,16 +1316,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1232,16 +1336,16 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1252,16 +1356,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1272,10 +1376,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -1292,10 +1396,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1312,10 +1416,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -1332,13 +1436,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>43</v>
@@ -1350,76 +1454,76 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>50</v>
-      </c>
       <c r="C20" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" s="0" t="s">
         <v>48</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1441,7 +1545,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1449,13 +1553,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1467,18 +1570,18 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1487,13 +1590,13 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,25 +1604,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1527,25 +1630,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1553,25 +1656,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,25 +1682,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1605,13 +1708,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>7</v>
@@ -1623,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1631,13 +1734,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>9</v>
@@ -1649,7 +1752,7 @@
         <v>20</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1657,10 +1760,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>15</v>
@@ -1675,7 +1778,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1683,16 +1786,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1</v>
@@ -1701,7 +1804,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1709,25 +1812,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1735,25 +1838,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1761,13 +1864,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>11</v>
@@ -1776,10 +1879,10 @@
         <v>0.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1787,25 +1890,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>0.1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1813,7 +1916,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>82</v>
@@ -1828,10 +1931,10 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1839,16 +1942,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>0.1</v>
@@ -1857,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1865,13 +1968,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>87</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>9</v>
@@ -1883,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1894,7 +1997,7 @@
         <v>91</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -1909,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1920,13 +2023,13 @@
         <v>92</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.1</v>
@@ -1935,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1943,13 +2046,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>11</v>
@@ -1961,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,42 +2072,120 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="8" t="s">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>1086</v>
-      </c>
-      <c r="H24" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="H27" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2018,4 +2199,169 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4885</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5862</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3908</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 23-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 23-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 24-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 24-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,12 +44,12 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <i val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -59,7 +59,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -81,6 +81,11 @@
     </font>
     <font>
       <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -151,17 +156,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 23/07/2026 (20j). Livree. lun-sam. Mise a jour 23/07/2026.</t>
+          <t>01/07 au 24/07/2026 (21j). Livree. lun-sam. Mise a jour 24/07/2026.</t>
         </is>
       </c>
     </row>
@@ -574,7 +579,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 22/07</t>
+          <t>Evolution vs 23/07</t>
         </is>
       </c>
     </row>
@@ -590,14 +595,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1272.2</v>
+        <v>1398.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>63.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+3.0 t/j</t>
         </is>
       </c>
     </row>
@@ -613,14 +618,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>733.7</v>
+        <v>807.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>36.7</v>
+        <v>38.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-1.9 t/j</t>
+          <t>+1.8 t/j</t>
         </is>
       </c>
     </row>
@@ -636,14 +641,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>576.2</v>
+        <v>583.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>28.8</v>
+        <v>27.8</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+0.8 t/j</t>
+          <t>-1.0 t/j</t>
         </is>
       </c>
     </row>
@@ -659,14 +664,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>429.3</v>
+        <v>474.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>22.6</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+1.1 t/j</t>
         </is>
       </c>
     </row>
@@ -682,14 +687,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>317.7</v>
+        <v>330.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>+0.3 t/j</t>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -705,14 +710,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>275.4</v>
+        <v>285.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>-0.3 t/j</t>
+        <v>13.6</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -728,14 +733,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>238.1</v>
+        <v>239.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+0.9 t/j</t>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -751,60 +756,60 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>210.7</v>
+        <v>228.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>+0.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>197.9</v>
+        <v>207.9</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>180.2</v>
+        <v>199.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-0.2 t/j</t>
+        <v>9.5</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -820,12 +825,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>126.9</v>
+        <v>129</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+        <v>6.1</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>-0.2 t/j</t>
         </is>
@@ -834,46 +839,46 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>116.6</v>
+        <v>127.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>6.1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+0.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>115.9</v>
+        <v>125.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -889,14 +894,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>60.6</v>
+        <v>64.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -912,10 +917,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2166.1</v>
+        <v>2312.2</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>108.3</v>
+        <v>110.1</v>
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1317.3</v>
+        <v>1392</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -950,10 +955,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1368.1</v>
+        <v>1498.5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>68.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -965,14 +970,14 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>4851.4</v>
+        <v>5202.7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>242.6</v>
+        <v>247.7</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>-1.7 t/j vs 244.2</t>
+          <t>+5.2 t/j vs 242.6</t>
         </is>
       </c>
     </row>
@@ -986,14 +991,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 242.6 t/j (4851 sacs) sur 20j.</t>
+          <t>Moyenne/jour globale: 247.7 t/j (4954 sacs) sur 21j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (22/07): 244.2 t/j (4884 sacs) sur 19j.</t>
+          <t>Precedent (23/07): 242.6 t/j (4851 sacs) sur 20j.</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1023,14 +1028,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 23/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 24/07/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 23/07/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 24/07/2026.</t>
         </is>
       </c>
     </row>
@@ -1067,76 +1072,76 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 22/07</t>
+          <t>Evolution cmdes vs 23/07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
+          <t>4.4:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>-10 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>5.5:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1145,91 +1150,91 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>0.6:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.4:1</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>3.2:1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1248,143 +1253,143 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.6:1</t>
+          <t>1.6:1</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>1.1:1</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1393,10 +1398,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
@@ -1408,14 +1413,14 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1424,140 +1429,156 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>0.9:1</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>0.6:1</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Nkongsamba</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>-17 cmdes vs 92</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>-5 cmdes vs 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>79%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>63%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>&gt; 20:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -1569,17 +1590,32 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le 23/07/2026 correspond au 1er jour d'application de l'augmentation +2 000 XAF/sac soja.</t>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.6:1 (vs 2.5:1 le 22/07).</t>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 1.7:1 (vs 2.6:1 le 23/07).</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1611,7 +1647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 23/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1701,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 22/07</t>
+          <t>Nouveau vs 23/07</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1711,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125378</t>
+          <t>SO2607-125573</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00943 -  PROVENDERIE QUEEN FEET</t>
+          <t>PRADU-COOP CA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1694,17 +1730,17 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1716,22 +1752,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125387</t>
+          <t>SO2607-125566</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00216 -  DR LARISSA</t>
+          <t>CU2407-00990 -  ENOCH ELIJAH (ETS ELIBOY FORTUNE FARM)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -1745,7 +1781,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1757,22 +1793,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125416</t>
+          <t>SO2607-125582</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2502-01249 -  PROVENDERIE DE L'ASSURANCE (NOUWOU FOZEU FRANCO)</t>
+          <t>CU2606-14501 -  MBEUMO GASTON</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -1786,7 +1822,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1798,22 +1834,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125506</t>
+          <t>SO2607-125675</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00902 -  M MBOZEKO MATHURIN</t>
+          <t>PROVOCAM COOP-CA.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -1827,7 +1863,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1839,36 +1875,36 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125365</t>
+          <t>SO2607-125703</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1880,36 +1916,36 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125401</t>
+          <t>SO2607-125695</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1921,36 +1957,36 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125414</t>
+          <t>SO2607-125610</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -1962,440 +1998,71 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125524</t>
+          <t>SO2607-125718</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125409</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125482</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125367</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 8 cmdes (9.2 t) le 24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125395</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125449</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125457</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125494</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125532</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125539</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 17 cmdes (5.7 t) le 23/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (22/07): 22 cmdes (10.3 t)</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (23/07): 17 cmdes (5.7 t)</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2098,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (242.6 t/j, Livree). Mise a jour 23/07/2026.</t>
+          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (247.7 t/j, Livree). Mise a jour 24/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2474,22 +2141,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4851</v>
+        <v>4955</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>242.6</v>
+        <v>247.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+0 jours vs 29/08/2026</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>-1 jours vs 31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2167,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5822</v>
+        <v>5946</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>291.1</v>
+        <v>297.3</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>27</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>+0 jours vs 22/08/2026</t>
+          <t>+0 jours vs 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2526,22 +2193,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3881</v>
+        <v>3964</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>194.1</v>
+        <v>198.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+0 jours vs 08/09/2026</t>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-1 jours vs 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2244,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>97 029 sacs</t>
+          <t>104 053 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>4851.4 t</t>
+          <t>5202.7 t</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2261,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4 851 sacs</t>
+          <t>4 955 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>242.6 t</t>
+          <t>247.7 t</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2291,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -2645,14 +2312,14 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: La moyenne journaliere est remontee a 242.6 t/j (vs 244.2 t/j au 22/07).</t>
+          <t>ANALYSE: La moyenne journaliere est remontee a 247.7 t/j (vs 242.6 t/j au 23/07).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>La legere baisse (-1.6 t/j) reste dans la marge de fluctuation hebdomadaire.</t>
+          <t>Hausse de +5.2 t/j — pas d'effet visible de la hausse de prix pour le moment.</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2333,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 31/08/2026 (33 jours de stock).</t>
+          <t>Date de rupture probable: 31/08/2026 (32 jours de stock).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 24-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 24-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 25-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 25-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -59,7 +59,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -76,17 +76,17 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -162,10 +162,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 24/07/2026 (21j). Livree. lun-sam. Mise a jour 24/07/2026.</t>
+          <t>01/07 au 27/07/2026 (23j). Livree. lun-sam. Mise a jour 27/07/2026.</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 23/07</t>
+          <t>Evolution vs 24/07</t>
         </is>
       </c>
     </row>
@@ -595,14 +595,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1398.8</v>
+        <v>1550.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>+3.0 t/j</t>
+          <t>+0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -621,11 +621,11 @@
         <v>807.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>+1.8 t/j</t>
+        <v>35.1</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-3.3 t/j</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
         <v>583.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>27.8</v>
+        <v>25.4</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>-1.0 t/j</t>
+          <t>-2.4 t/j</t>
         </is>
       </c>
     </row>
@@ -664,14 +664,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>474.7</v>
+        <v>480.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+1.1 t/j</t>
+        <v>20.9</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>-1.7 t/j</t>
         </is>
       </c>
     </row>
@@ -687,14 +687,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>330.1</v>
+        <v>370.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>-0.2 t/j</t>
+        <v>16.1</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>285.6</v>
+        <v>295.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>-0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -733,14 +733,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>239.8</v>
+        <v>257.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -756,14 +756,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>228.5</v>
+        <v>240.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>+0.3 t/j</t>
+        <v>10.4</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -779,14 +779,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>207.9</v>
+        <v>215.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+        <v>9.4</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -802,60 +802,60 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>199.3</v>
+        <v>206.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>129</v>
+        <v>133.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>127.8</v>
+        <v>131.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>+0.3 t/j</t>
+        <v>5.7</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>125.6</v>
+        <v>127.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+        <v>5.6</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -897,11 +897,11 @@
         <v>64.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>+0.1 t/j</t>
+        <v>2.8</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2312.2</v>
+        <v>2503.5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>110.1</v>
+        <v>108.8</v>
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1392</v>
+        <v>1438.5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>66.3</v>
+        <v>62.5</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1498.5</v>
+        <v>1522.5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -970,14 +970,14 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>5202.7</v>
+        <v>5464.5</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>247.7</v>
+        <v>237.6</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>+5.2 t/j vs 242.6</t>
+          <t>-10.2 t/j vs 247.7</t>
         </is>
       </c>
     </row>
@@ -991,14 +991,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 247.7 t/j (4954 sacs) sur 21j.</t>
+          <t>Moyenne/jour globale: 237.6 t/j (4751 sacs) sur 23j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (23/07): 242.6 t/j (4851 sacs) sur 20j.</t>
+          <t>Precedent (24/07): 247.7 t/j (4954 sacs) sur 21j.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1028,14 +1028,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 24/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 25/07/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 24/07/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 27/07/2026.</t>
         </is>
       </c>
     </row>
@@ -1072,76 +1072,76 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 23/07</t>
+          <t>Evolution cmdes vs 24/07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>4.4:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>+6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1150,65 +1150,65 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>0.6:1</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>-5 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -1222,81 +1222,81 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1.6:1</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>3.3:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1305,20 +1305,20 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>+1 cmdes</t>
         </is>
@@ -1327,22 +1327,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -1351,14 +1351,14 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1367,60 +1367,60 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1.1:1</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1429,156 +1429,140 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>0.6:1</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Nkongsamba</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>1.7:1</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>-5 cmdes vs 75</t>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>-4 cmdes vs 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -1590,32 +1574,24 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 1.7:1 (vs 2.6:1 le 23/07).</t>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.1:1 (vs 1.7:1 le 24/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 25/07 (dernier jour complet, 66 cmdes soja). Le 27/07 est une extraction matinale (85 lignes au total, 0 commande soja Livree).</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1623,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 24/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 25/07/2026</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1677,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 23/07</t>
+          <t>Nouveau vs 24/07</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1687,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125573</t>
+          <t>SO2607-125835</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>PRADU-COOP CA</t>
+          <t>CU2407-00902 -  M MBOZEKO MATHURIN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1730,10 +1706,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1752,29 +1728,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125566</t>
+          <t>SO2607-125859</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00990 -  ENOCH ELIJAH (ETS ELIBOY FORTUNE FARM)</t>
+          <t>CU2502-01224 -  PROVENDERIE YVESCAM</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -1793,29 +1769,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125582</t>
+          <t>SO2607-125820</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2606-14501 -  MBEUMO GASTON</t>
+          <t>CU2504-01301 -  GIC NKOUNA</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1834,22 +1810,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125675</t>
+          <t>SO2607-125743</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>PROVOCAM COOP-CA.</t>
+          <t>CU2407-00198 -  ROCHE KENGNE RAYMOND</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -1875,22 +1851,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125703</t>
+          <t>SO2607-125795</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2604-14454 -  DACOSTA POULTRY FARM (JETIMONEH OLIVER NKATOH)</t>
+          <t>CU2407-00220 -  FON EMMANUEL FOKUM</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -1916,17 +1892,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125695</t>
+          <t>SO2607-125869</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+          <t>CU2407-00224 -  TCHOFFO HILAIRE HONORE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1935,10 +1911,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1957,29 +1933,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125610</t>
+          <t>SO2607-125753</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1998,71 +1974,399 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125718</t>
+          <t>SO2607-125851</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125749</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Bertoua</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125764</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Bertoua</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125769</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125780</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Famla</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125844</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Bertoua</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125787</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125842</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125858</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>184</v>
-      </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 8 cmdes (9.2 t) le 24/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (23/07): 17 cmdes (5.7 t)</t>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 16 cmdes (10.7 t) le 25/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (24/07): 8 cmdes (9.2 t)</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2402,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (247.7 t/j, Livree). Mise a jour 24/07/2026.</t>
+          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (237.6 t/j, Livree). Mise a jour 27/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2141,22 +2445,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4955</v>
+        <v>4752</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>247.7</v>
+        <v>237.6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>-1 jours vs 31/08/2026</t>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+2 jours vs 31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2167,22 +2471,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5946</v>
+        <v>5702</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>297.3</v>
+        <v>285.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+0 jours vs 24/08/2026</t>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+1 jours vs 25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2193,27 +2497,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3964</v>
+        <v>3801</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>198.2</v>
+        <v>190.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>-1 jours vs 09/09/2026</t>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+2 jours vs 09/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2244,12 +2548,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>104 053 sacs</t>
+          <t>109 290 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>5202.7 t</t>
+          <t>5464.5 t</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2565,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4 955 sacs</t>
+          <t>4 752 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>247.7 t</t>
+          <t>237.6 t</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2595,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -2312,14 +2616,14 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: La moyenne journaliere est remontee a 247.7 t/j (vs 242.6 t/j au 23/07).</t>
+          <t>ANALYSE: La moyenne journaliere est remontee a 237.6 t/j (vs 247.7 t/j au 24/07).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Hausse de +5.2 t/j — pas d'effet visible de la hausse de prix pour le moment.</t>
+          <t>Baisse de 10.2 t/j — a surveiller (effet possible de la hausse de prix).</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2637,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 31/08/2026 (32 jours de stock).</t>
+          <t>Date de rupture probable: 04/09/2026 (34 jours de stock).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 25-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 25-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 27-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 27-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,7 +59,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -76,17 +76,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -162,11 +158,11 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 27/07/2026 (23j). Livree. lun-sam. Mise a jour 27/07/2026.</t>
+          <t>01/07 au 28/07/2026 (24j). Livree. lun-sam. Mise a jour 28/07/2026.</t>
         </is>
       </c>
     </row>
@@ -579,7 +575,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 24/07</t>
+          <t>Evolution vs 27/07</t>
         </is>
       </c>
     </row>
@@ -595,14 +591,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1550.2</v>
+        <v>1686</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>+0.8 t/j</t>
+          <t>+2.9 t/j</t>
         </is>
       </c>
     </row>
@@ -618,14 +614,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>807.6</v>
+        <v>933.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>-3.3 t/j</t>
+        <v>38.9</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+3.8 t/j</t>
         </is>
       </c>
     </row>
@@ -641,14 +637,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>583.2</v>
+        <v>705.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>-2.4 t/j</t>
+        <v>29.4</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+4.0 t/j</t>
         </is>
       </c>
     </row>
@@ -664,14 +660,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>480.6</v>
+        <v>513.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>-1.7 t/j</t>
+        <v>21.4</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -687,14 +683,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>370.1</v>
+        <v>383.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>+0.4 t/j</t>
+        <v>16</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -710,14 +706,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>295.6</v>
+        <v>312.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>-0.8 t/j</t>
+        <v>13</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -733,14 +729,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>257.9</v>
+        <v>267.9</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>-0.2 t/j</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -756,60 +752,60 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>240.2</v>
+        <v>249.6</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>-0.4 t/j</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>215.6</v>
+        <v>215.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>-0.5 t/j</t>
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>206.1</v>
+        <v>215.6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -825,14 +821,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>133.5</v>
+        <v>137.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>-0.3 t/j</t>
+        <v>5.7</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -848,14 +844,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>131.5</v>
+        <v>134.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>-0.4 t/j</t>
+        <v>5.6</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -874,11 +870,11 @@
         <v>127.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -894,14 +890,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.8</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>-0.3 t/j</t>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -917,10 +913,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2503.5</v>
+        <v>2774.8</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>108.8</v>
+        <v>115.6</v>
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
@@ -936,10 +932,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1438.5</v>
+        <v>1515.7</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>62.5</v>
+        <v>63.2</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -955,10 +951,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1522.5</v>
+        <v>1661.4</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>66.2</v>
+        <v>69.2</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -970,14 +966,14 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>5464.5</v>
+        <v>5951.9</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>237.6</v>
+        <v>248</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>-10.2 t/j vs 247.7</t>
+          <t>+10.4 t/j vs 237.6</t>
         </is>
       </c>
     </row>
@@ -991,14 +987,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 237.6 t/j (4751 sacs) sur 23j.</t>
+          <t>Moyenne/jour globale: 248.0 t/j (4959 sacs) sur 24j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (24/07): 247.7 t/j (4954 sacs) sur 21j.</t>
+          <t>Precedent (27/07): 237.6 t/j (4751 sacs) sur 23j.</t>
         </is>
       </c>
     </row>
@@ -1028,14 +1024,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 25/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 27/07/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 27/07/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 28/07/2026.</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1068,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 24/07</t>
+          <t>Evolution cmdes vs 27/07</t>
         </is>
       </c>
     </row>
@@ -1088,29 +1084,29 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>3.1:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+6 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1119,29 +1115,29 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
+          <t>4.6:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>+4 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1153,26 +1149,26 @@
         <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>2.2:1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>+7 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1181,60 +1177,60 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>3.1:1</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>3.0:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1243,84 +1239,84 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>3.6:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.3:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>0.5:1</t>
+          <t>1.5:1</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
@@ -1336,29 +1332,29 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>3.4:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1367,29 +1363,29 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-1 cmdes</t>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1398,34 +1394,34 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1439,12 +1435,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>0.7:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
@@ -1456,27 +1452,27 @@
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>2.1:1</t>
+          <t>2.9:1</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>-4 cmdes vs 70</t>
+          <t>+108 cmdes vs 0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
@@ -1506,11 +1502,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>59%</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1517,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1532,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1547,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
@@ -1584,14 +1580,14 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Ratio global: 2.1:1 (vs 1.7:1 le 24/07).</t>
+          <t>Ratio global: 2.9:1 (vs ∞ le 27/07).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 25/07 (dernier jour complet, 66 cmdes soja). Le 27/07 est une extraction matinale (85 lignes au total, 0 commande soja Livree).</t>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 27/07 (dernier jour complet, 108 cmdes soja). Le 28/07 est une extraction matinale (11 lignes au total).</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1623,7 +1619,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 25/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1673,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 24/07</t>
+          <t>Nouveau vs 27/07</t>
         </is>
       </c>
     </row>
@@ -1687,29 +1683,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125835</t>
+          <t>SO2607-125976</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00902 -  M MBOZEKO MATHURIN</t>
+          <t>CU2406-00020 -  PROVENDERIE RENOUVEAU 14</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1728,17 +1724,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125859</t>
+          <t>SO2607-126033</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2502-01224 -  PROVENDERIE YVESCAM</t>
+          <t>CU2407-00216 -  DR LARISSA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1769,17 +1765,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125820</t>
+          <t>SO2607-126097</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01301 -  GIC NKOUNA</t>
+          <t>CU2407-00987 -  SUCEES VIT</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1788,10 +1784,10 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1810,29 +1806,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125743</t>
+          <t>SO2607-125937</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00198 -  ROCHE KENGNE RAYMOND</t>
+          <t>CU2407-00162 -  FOTSING PIERRE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1851,29 +1847,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125795</t>
+          <t>SO2607-126075</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00220 -  FON EMMANUEL FOKUM</t>
+          <t>CU2407-00159 -  SIGNE WILLIAM</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -1892,12 +1888,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125869</t>
+          <t>SO2607-125922</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00224 -  TCHOFFO HILAIRE HONORE</t>
+          <t>CU2509-14109 -  TSAGUE RODRIGUE MAGLOIRE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1933,29 +1929,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125753</t>
+          <t>SO2607-125926</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2502-01249 -  PROVENDERIE DE L'ASSURANCE (NOUWOU FOZEU FRANCO)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1974,29 +1970,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125851</t>
+          <t>SO2607-125961</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+          <t>CU2407-00875 -  NOUMSI BLAISE</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2015,17 +2011,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125749</t>
+          <t>SO2607-126013</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-01020 -  FERME MOGOUONG THÉRÈSE</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2034,10 +2030,10 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -2056,17 +2052,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125764</t>
+          <t>SO2607-125938</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00138 -  CLIENTS COMPTOIR AHALA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2075,10 +2071,10 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -2097,17 +2093,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125769</t>
+          <t>SO2607-126065</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2116,10 +2112,10 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -2138,29 +2134,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125780</t>
+          <t>SO2607-125907</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -2179,17 +2175,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125844</t>
+          <t>SO2607-125925</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2198,10 +2194,10 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -2220,29 +2216,29 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125787</t>
+          <t>SO2607-126028</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -2261,17 +2257,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125842</t>
+          <t>SO2607-126003</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2280,10 +2276,10 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -2302,71 +2298,235 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125858</t>
+          <t>SO2607-125908</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>Ndobo</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125921</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Nkoabang</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-125983</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Bertoua</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126056</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
           <t>Ngaoundere</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126054</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Nkolbisson</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>213</v>
-      </c>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 16 cmdes (10.7 t) le 25/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (24/07): 8 cmdes (9.2 t)</t>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>281</v>
+      </c>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 20 cmdes (14.1 t) le 27/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (27/07): 0 cmdes (0.0 t)</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (237.6 t/j, Livree). Mise a jour 27/07/2026.</t>
+          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (248.0 t/j, Livree). Mise a jour 28/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2445,22 +2605,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4752</v>
+        <v>4960</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>237.6</v>
+        <v>248</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>+2 jours vs 31/08/2026</t>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>-2 jours vs 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2471,22 +2631,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5702</v>
+        <v>5952</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>285.1</v>
+        <v>297.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>28/08/2026</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+1 jours vs 25/08/2026</t>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>-1 jours vs 28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2497,27 +2657,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3801</v>
+        <v>3968</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>190.1</v>
+        <v>198.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>+2 jours vs 09/09/2026</t>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-2 jours vs 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2548,12 +2708,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>109 290 sacs</t>
+          <t>119 038 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>5464.5 t</t>
+          <t>5951.9 t</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2725,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4 752 sacs</t>
+          <t>4 960 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>237.6 t</t>
+          <t>248.0 t</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2755,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -2616,14 +2776,14 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: La moyenne journaliere est remontee a 237.6 t/j (vs 247.7 t/j au 24/07).</t>
+          <t>ANALYSE: La moyenne journaliere est remontee a 248.0 t/j (vs 237.6 t/j au 27/07).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Baisse de 10.2 t/j — a surveiller (effet possible de la hausse de prix).</t>
+          <t>Hausse de +10.4 t/j — pas d'effet visible de la hausse de prix pour le moment.</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2797,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 04/09/2026 (34 jours de stock).</t>
+          <t>Date de rupture probable: 03/09/2026 (32 jours de stock).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -2541,11 +2541,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2562,7 +2562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>160 000 sacs (8 000 t). Moy/jour sur juillet (248.0 t/j, Livree). Mise a jour 28/07/2026.</t>
+          <t>Stock physique au 21/07/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 21/07/2026→28/07/2026 deduites du stock. Mise a jour 28/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sacs/jour</t>
+          <t>Sacs/jour (post-stock)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2605,22 +2605,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4960</v>
+        <v>2985</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>248</v>
+        <v>149.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>-2 jours vs 04/09/2026</t>
+          <t>-14 jours vs 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -2631,22 +2631,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5952</v>
+        <v>3582</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>297.6</v>
+        <v>179.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>-1 jours vs 28/08/2026</t>
+          <t>-12 jours vs 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -2657,22 +2657,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3968</v>
+        <v>2388</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>198.4</v>
+        <v>119.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>-2 jours vs 14/09/2026</t>
+          <t>-18 jours vs 26/10/2026</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Stock initial (au 21/07)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2696,53 +2696,53 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>8 000 t</t>
+          <t>8000 t</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ventes juillet</t>
+          <t>Ventes post-stock 22→28/07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>119 038 sacs</t>
+          <t>17 909 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>5951.9 t</t>
+          <t>895.4 t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Moyenne/jour</t>
+          <t>Stock restant au 28/07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4 960 sacs</t>
+          <t>142 091 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>248.0 t</t>
+          <t>7104.6 t</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jours ouvrables</t>
+          <t>Jours ouvrables post-stock</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6j/sem (lun-sam)</t>
+          <t>6 j (lun-sam)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -2750,54 +2750,82 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Depart</t>
+          <t>Moyenne/jour post-stock</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
+          <t>2 984 sacs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>149.2 t</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Ventes juillet (total, info)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>119 038 sacs</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>5951.9 t</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Hausse prix soja</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>+2 000 XAF/sac le 23/07/2026</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: La moyenne journaliere est remontee a 248.0 t/j (vs 237.6 t/j au 27/07).</t>
-        </is>
-      </c>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Hausse de +10.4 t/j — pas d'effet visible de la hausse de prix pour le moment.</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock restant au 28/07/2026 = 142 091 sacs (7104.6 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>L'effet plein de la hausse +2 000 XAF/sac (effective 23/07) sera visible sur les jours a venir.</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Hausse moy/jour post-stock (+29.9 t/j) — pas d'effet visible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 03/09/2026 (32 jours de stock).</t>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Seules les ventes 22→28/07 (post-stock) sont deduites du stock pour calculer le stock restant au 28/07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 22/09/2026 (48 jours de stock restant).</t>
         </is>
       </c>
     </row>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 27-07" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 27-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Juillet" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +90,19 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +127,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +185,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -237,6 +262,322 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tendance journalière — Soja vs Concentrés (Juillet 2026)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'T5 - Tendance Juillet'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1F4E78"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$D$5:$D$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'T5 - Tendance Juillet'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C9A961"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$E$5:$E$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Tonnes</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Ratio soja:concentrés par jour (objectif 3:1)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'T5 - Tendance Juillet'!G4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'T5 - Tendance Juillet'!$G$5:$G$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Ratio (soja:conc)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2832,4 +3173,918 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TABLEAU 5 - Tendance journalière SOJA et CONCENTRÉS (Juillet 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Données Livrées au 28/07/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Jour sem.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Soja (t)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Concentrés (t)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Ratio soja:conc</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Ratio numérique</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>4.51:1</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>233.1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>3.5:1</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>5.55:1</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>5.99:1</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>4.01:1</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>5.29:1</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>5.5:1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>4.81:1</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>4.33:1</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>3.39:1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>4.43:1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>285.3</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>3.88:1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>4.02:1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>7.34:1</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>4.51:1</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>7.87:1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>3.97:1</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>3.08:1</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>3.07:1</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>2.77:1</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2.09:1</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2.33:1</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dim</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>205.4</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>2.85:1</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>NOTES DE LECTURE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début juillet) puis +2 000 FCFA/sac (23/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 27-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 27-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 28-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 28-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Juillet" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,13 +77,22 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -166,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,14 +189,15 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -312,12 +322,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$D$5:$D$32</f>
+              <f>'T5 - Tendance Juillet'!$D$5:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -347,12 +357,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$E$5:$E$32</f>
+              <f>'T5 - Tendance Juillet'!$E$5:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -459,12 +469,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$32</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$G$5:$G$32</f>
+              <f>'T5 - Tendance Juillet'!$G$5:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -889,7 +899,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 28/07/2026 (24j). Livree. lun-sam. Mise a jour 28/07/2026.</t>
+          <t>01/07 au 29/07/2026 (25j). Livree. lun-sam. Mise a jour 29/07/2026.</t>
         </is>
       </c>
     </row>
@@ -916,7 +926,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 27/07</t>
+          <t>Evolution vs 28/07</t>
         </is>
       </c>
     </row>
@@ -932,14 +942,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1686</v>
+        <v>1774.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70.2</v>
+        <v>71</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>+2.9 t/j</t>
+          <t>+0.7 t/j</t>
         </is>
       </c>
     </row>
@@ -955,14 +965,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>933.6</v>
+        <v>1361.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>38.9</v>
+        <v>54.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>+3.8 t/j</t>
+          <t>+15.6 t/j</t>
         </is>
       </c>
     </row>
@@ -978,14 +988,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>705.5</v>
+        <v>725.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>+4.0 t/j</t>
+        <v>29</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1001,14 +1011,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>513.9</v>
+        <v>523</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+0.5 t/j</t>
+        <v>20.9</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1034,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>383.4</v>
+        <v>387.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1057,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>312.5</v>
+        <v>316.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+        <v>12.7</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>-0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1080,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>267.9</v>
+        <v>281.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1093,60 +1103,60 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>249.6</v>
+        <v>254.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>10.2</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>215.8</v>
+        <v>228.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>9.1</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>215.6</v>
+        <v>225.3</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>-0.4 t/j</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1172,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>137.6</v>
+        <v>143.7</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1195,12 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>134.9</v>
+        <v>136.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>-0.1 t/j</t>
         </is>
@@ -1208,14 +1218,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>127.7</v>
+        <v>131.6</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>-0.2 t/j</t>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1241,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.8</v>
@@ -1254,10 +1264,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2774.8</v>
+        <v>2887.8</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>115.6</v>
+        <v>115.5</v>
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
@@ -1273,10 +1283,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1515.7</v>
+        <v>1560</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>63.2</v>
+        <v>62.4</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1292,10 +1302,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1661.4</v>
+        <v>2112.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>69.2</v>
+        <v>84.5</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1307,14 +1317,14 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>5951.9</v>
+        <v>6560.5</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>248</v>
+        <v>262.4</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>+10.4 t/j vs 237.6</t>
+          <t>+14.4 t/j vs 248.0</t>
         </is>
       </c>
     </row>
@@ -1328,14 +1338,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 248.0 t/j (4959 sacs) sur 24j.</t>
+          <t>Moyenne/jour globale: 262.4 t/j (5248 sacs) sur 25j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (27/07): 237.6 t/j (4751 sacs) sur 23j.</t>
+          <t>Precedent (28/07): 248.0 t/j (4959 sacs) sur 24j.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1365,14 +1375,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 27/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 28/07/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 28/07/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 29/07/2026.</t>
         </is>
       </c>
     </row>
@@ -1425,13 +1435,13 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1440,14 +1450,14 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>+16 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1456,29 +1466,29 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>4.6:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1487,44 +1497,44 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-10 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -1533,67 +1543,67 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
+          <t>3.9:1</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>nouveau</t>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>3.6:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>nouveau</t>
         </is>
@@ -1602,131 +1612,131 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1735,20 +1745,20 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>nouveau</t>
         </is>
@@ -1757,149 +1767,165 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ahala</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-5 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>+108 cmdes vs 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>-3 cmdes vs 108</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>59%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>63%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>&gt; 20:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -1911,24 +1937,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.9:1 (vs ∞ le 27/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 27/07 (dernier jour complet, 108 cmdes soja). Le 28/07 est une extraction matinale (11 lignes au total).</t>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.2:1 (vs 2.9:1 le 27/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 28/07 (dernier jour complet, 105 cmdes soja). Comparaison vs 27/07 (108 cmdes, extraction precedente matinale sans 28/07). Le 29/07 est aussi une extraction matinale (182 lignes au total).</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1960,7 +2001,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 27/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2024,29 +2065,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125976</t>
+          <t>SO2607-126282</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00020 -  PROVENDERIE RENOUVEAU 14</t>
+          <t>CU2407-00518 -  DJEM JOSEPH</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2065,29 +2106,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126033</t>
+          <t>SO2607-126159</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00216 -  DR LARISSA</t>
+          <t>CU2407-00676 -  KAMGO</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2106,17 +2147,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126097</t>
+          <t>SO2607-126333</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00987 -  SUCEES VIT</t>
+          <t>CU2509-14122 -  CORART FARM (tchamokouen cheping arthur Rodrigue)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2125,10 +2166,10 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -2147,29 +2188,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125937</t>
+          <t>SO2607-126343</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00162 -  FOTSING PIERRE</t>
+          <t>CU2407-00221 -  Dr TCHOFFO KAFO ERNEST ALBIN</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -2188,29 +2229,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126075</t>
+          <t>SO2607-126173</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00159 -  SIGNE WILLIAM</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.1</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -2229,17 +2270,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125922</t>
+          <t>SO2607-126266</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2509-14109 -  TSAGUE RODRIGUE MAGLOIRE</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2248,10 +2289,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -2270,29 +2311,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125926</t>
+          <t>SO2607-126210</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2502-01249 -  PROVENDERIE DE L'ASSURANCE (NOUWOU FOZEU FRANCO)</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -2311,29 +2352,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125961</t>
+          <t>SO2607-126309</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00875 -  NOUMSI BLAISE</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -2352,29 +2393,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126013</t>
+          <t>SO2607-126330</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2407-01020 -  FERME MOGOUONG THÉRÈSE</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -2393,29 +2434,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125938</t>
+          <t>SO2607-126353</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00138 -  CLIENTS COMPTOIR AHALA</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -2434,29 +2475,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126065</t>
+          <t>SO2607-126146</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -2475,29 +2516,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125907</t>
+          <t>SO2607-126243</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -2516,29 +2557,29 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SO2607-125925</t>
+          <t>SO2607-126256</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00145 -  CLIENTS COMPTOIR MESSASSI</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -2557,29 +2598,29 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126028</t>
+          <t>SO2607-126365</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -2598,17 +2639,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126003</t>
+          <t>SO2607-126261</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2617,10 +2658,10 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -2634,240 +2675,35 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125908</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Ndobo</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125921</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Nkoabang</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-125983</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Bertoua</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 15 cmdes (6.4 t) le 28/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126056</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126054</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Nkolbisson</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>281</v>
-      </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 20 cmdes (14.1 t) le 27/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (27/07): 0 cmdes (0.0 t)</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (27/07): 20 cmdes (14.1 t)</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2739,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 21/07/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 21/07/2026→28/07/2026 deduites du stock. Mise a jour 28/07/2026.</t>
+          <t>Stock physique au 21/07/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 21/07/2026→29/07/2026 deduites du stock. Mise a jour 29/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2946,22 +2782,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2985</v>
+        <v>3174</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>149.2</v>
+        <v>158.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>-14 jours vs 07/10/2026</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>-5 jours vs 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -2972,22 +2808,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3582</v>
+        <v>3809</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>179.1</v>
+        <v>190.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>-12 jours vs 25/09/2026</t>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>-4 jours vs 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -2998,27 +2834,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2388</v>
+        <v>2539</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>119.4</v>
+        <v>127</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-18 jours vs 26/10/2026</t>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>-6 jours vs 06/10/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -3044,34 +2880,34 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ventes post-stock 22→28/07</t>
+          <t>Ventes post-stock 22→29/07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>17 909 sacs</t>
+          <t>22 219 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>895.4 t</t>
+          <t>1111.0 t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Stock restant au 28/07</t>
+          <t>Stock restant au 29/07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>142 091 sacs</t>
+          <t>137 781 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7104.6 t</t>
+          <t>6889.0 t</t>
         </is>
       </c>
     </row>
@@ -3083,7 +2919,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6 j (lun-sam)</t>
+          <t>7 j (lun-sam)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -3096,12 +2932,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2 984 sacs</t>
+          <t>3 174 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>149.2 t</t>
+          <t>158.7 t</t>
         </is>
       </c>
     </row>
@@ -3113,12 +2949,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>119 038 sacs</t>
+          <t>131 210 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>5951.9 t</t>
+          <t>6560.5 t</t>
         </is>
       </c>
     </row>
@@ -3138,35 +2974,35 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 28/07/2026 = 142 091 sacs (7104.6 t).</t>
+          <t>ANALYSE: Stock restant au 29/07/2026 = 137 781 sacs (6889.0 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hausse moy/jour post-stock (+29.9 t/j) — pas d'effet visible de la hausse de prix.</t>
+          <t>Hausse moy/jour post-stock (+9.5 t/j) — pas d'effet visible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Seules les ventes 22→28/07 (post-stock) sont deduites du stock pour calculer le stock restant au 28/07.</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Seules les ventes 22→29/07 (post-stock) sont deduites du stock pour calculer le stock restant au 29/07.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 22/09/2026 (48 jours de stock restant).</t>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 17/09/2026 (43 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3203,7 +3039,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 28/07/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 29/07/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3288,18 +3124,18 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>233.1</v>
+        <v>353.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>66.5</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3.5:1</t>
+          <t>5.31:1</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="7">
@@ -3361,26 +3197,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3459,18 +3295,18 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>383.7</v>
+        <v>453.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>69.7</v>
+        <v>70.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>5.5:1</t>
+          <t>6.42:1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5.5</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="13">
@@ -3517,10 +3353,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>238.7</v>
+        <v>240.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>55.1</v>
+        <v>55.6</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -3546,10 +3382,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>117</v>
+        <v>118.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -3561,26 +3397,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3601,18 +3437,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>318.8</v>
+        <v>345.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>72</v>
+        <v>75.5</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>4.43:1</t>
+          <t>4.57:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4.43</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="18">
@@ -3630,18 +3466,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>285.3</v>
+        <v>290.3</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>73.5</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>3.88:1</t>
+          <t>3.95:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="19">
@@ -3662,15 +3498,15 @@
         <v>239.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>59.6</v>
+        <v>60.3</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>4.02:1</t>
+          <t>3.98:1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="20">
@@ -3688,18 +3524,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>379.7</v>
+        <v>462.6</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>51.7</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7.34:1</t>
+          <t>8.95:1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.34</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3746,41 +3582,41 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>298.2</v>
+        <v>300.2</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>37.9</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7.87:1</t>
+          <t>7.93:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7.87</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3801,18 +3637,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>367.3</v>
+        <v>414</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>92.5</v>
+        <v>96.8</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>3.97:1</t>
+          <t>4.28:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3.97</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="25">
@@ -3830,18 +3666,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>248.4</v>
+        <v>284.9</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>80.5</v>
+        <v>91</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>3.08:1</t>
+          <t>3.13:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="26">
@@ -3859,41 +3695,41 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>257.9</v>
+        <v>278.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>3.07:1</t>
+          <t>3.0:1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
-        <v>206.9</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="D27" s="18" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>2.77:1</t>
         </is>
@@ -3917,18 +3753,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>115.9</v>
+        <v>121.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>55.5</v>
+        <v>57.6</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2.09:1</t>
+          <t>2.11:1</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="29">
@@ -3946,41 +3782,41 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>109.3</v>
+        <v>138.8</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>46.9</v>
+        <v>51.3</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2.33:1</t>
+          <t>2.71:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4001,18 +3837,18 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>205.4</v>
+        <v>242.1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>72</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2.85:1</t>
+          <t>2.57:1</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="32">
@@ -4030,54 +3866,86 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0</v>
+        <v>108.4</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+          <t>2.24:1</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Mer</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1.67:1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début juillet) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 28-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 28-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 29-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 29-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Juillet" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -45,12 +45,12 @@
       <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <i val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
     <font>
@@ -183,8 +183,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -942,14 +942,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1774.8</v>
+        <v>1826.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>+0.7 t/j</t>
+          <t>-0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -965,14 +965,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1361.8</v>
+        <v>1420.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>+15.6 t/j</t>
+        <v>56.8</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -988,14 +988,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>725.5</v>
+        <v>775.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>+0.8 t/j</t>
         </is>
       </c>
     </row>
@@ -1011,14 +1011,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>523</v>
+        <v>541.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>-0.5 t/j</t>
+        <v>21.6</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1034,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>387.4</v>
+        <v>400.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>-0.5 t/j</t>
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1057,14 +1057,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>316.5</v>
+        <v>353.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>-0.4 t/j</t>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1080,14 +1080,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>281.5</v>
+        <v>293.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>+0.1 t/j</t>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1103,14 +1103,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>254.4</v>
+        <v>273.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>+0.4 t/j</t>
         </is>
       </c>
     </row>
@@ -1126,14 +1126,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>228.2</v>
+        <v>245.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>+0.1 t/j</t>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1149,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>225.3</v>
+        <v>226.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>9.1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>143.7</v>
+        <v>150.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>136.9</v>
+        <v>144.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>-0.1 t/j</t>
+        <v>5.8</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1218,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>131.6</v>
+        <v>141.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-0.1 t/j</t>
+        <v>5.6</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1241,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>70</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2887.8</v>
+        <v>3002.6</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>115.5</v>
+        <v>120.1</v>
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1560</v>
+        <v>1635.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>62.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>2112.8</v>
+        <v>2224.5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>84.5</v>
+        <v>89</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1317,14 +1317,14 @@
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>6560.5</v>
+        <v>6862.8</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>262.4</v>
+        <v>274.5</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>+14.4 t/j vs 248.0</t>
+          <t>+1.2 t/j vs 273.4</t>
         </is>
       </c>
     </row>
@@ -1338,14 +1338,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 262.4 t/j (5248 sacs) sur 25j.</t>
+          <t>Moyenne/jour globale: 274.5 t/j (5490 sacs) sur 25j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (28/07): 248.0 t/j (4959 sacs) sur 24j.</t>
+          <t>Precedent (28/07): 273.4 t/j (5467 sacs) sur 24j.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1375,7 +1375,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 28/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 29/07/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1419,38 +1419,38 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 27/07</t>
+          <t>Evolution cmdes vs 28/07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3.1:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>+16 cmdes</t>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
@@ -1476,69 +1476,69 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-10 cmdes</t>
+          <t>5.7:1</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3.1:1</t>
+          <t>3.2:1</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1550,38 +1550,38 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>3.9:1</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-41 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1593,143 +1593,143 @@
         <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>3.4:1</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>-1 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>0.8:1</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1.9:1</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>0.8:1</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
@@ -1758,28 +1758,28 @@
           <t>2.4:1</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
@@ -1789,16 +1789,16 @@
           <t>2.1:1</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1807,169 +1807,200 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1.7:1</t>
+          <t>3.1:1</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>-3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Djeleng</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ouest</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>0.8:1</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>nouveau</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2.2:1</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>-3 cmdes vs 108</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>2.4:1</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>-18 cmdes vs 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>63%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>73%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>10-20:1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>&gt; 20:1</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.2:1 (vs 2.9:1 le 27/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 28/07 (dernier jour complet, 105 cmdes soja). Comparaison vs 27/07 (108 cmdes, extraction precedente matinale sans 28/07). Le 29/07 est aussi une extraction matinale (182 lignes au total).</t>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.4:1 (vs 2.2:1 le 28/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 29/07 (87 cmdes soja Livrées). Comparaison vs 28/07 (105 cmdes, extraction precedente).</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2001,7 +2032,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 28/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2086,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 27/07</t>
+          <t>Nouveau vs 28/07</t>
         </is>
       </c>
     </row>
@@ -2065,36 +2096,36 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126282</t>
+          <t>SO2607-126570</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00518 -  DJEM JOSEPH</t>
+          <t>CU2502-01255 -  SIETCHIPING</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2106,36 +2137,36 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126159</t>
+          <t>SO2607-126410</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00676 -  KAMGO</t>
+          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2147,36 +2178,36 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126333</t>
+          <t>SO2607-126546</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2509-14122 -  CORART FARM (tchamokouen cheping arthur Rodrigue)</t>
+          <t>CU2407-00159 -  SIGNE WILLIAM</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2188,22 +2219,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126343</t>
+          <t>SO2607-126394</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00221 -  Dr TCHOFFO KAFO ERNEST ALBIN</t>
+          <t>CU2407-00353 -  PROVOCAM</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -2217,7 +2248,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2229,36 +2260,36 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126173</t>
+          <t>SO2607-126456</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2270,36 +2301,36 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126266</t>
+          <t>SO2607-126559</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2311,36 +2342,36 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126210</t>
+          <t>SO2607-126435</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2352,36 +2383,36 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126309</t>
+          <t>SO2607-126415</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2393,7 +2424,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126330</t>
+          <t>SO2607-126416</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2412,17 +2443,17 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2434,17 +2465,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126353</t>
+          <t>SO2607-126473</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2453,17 +2484,17 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2475,22 +2506,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126146</t>
+          <t>SO2607-126576</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -2504,7 +2535,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2516,17 +2547,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126243</t>
+          <t>SO2607-126547</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2535,175 +2566,52 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126256</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126365</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CU2406-00122 -  CLIENTS COMPTOIR FAMLA</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Famla</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126261</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Ngaoundere</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Total soja-only: 12 cmdes (9.6 t) le 29/07/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 15 cmdes (6.4 t) le 28/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (27/07): 20 cmdes (14.1 t)</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (28/07): 15 cmdes (6.4 t)</t>
         </is>
       </c>
     </row>
@@ -2782,22 +2690,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3174</v>
+        <v>3748</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>158.7</v>
+        <v>187.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>-5 jours vs 22/09/2026</t>
+          <t>-2 jours vs 10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2808,22 +2716,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3809</v>
+        <v>4497</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>190.5</v>
+        <v>224.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>-4 jours vs 12/09/2026</t>
+          <t>-1 jours vs 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2834,22 +2742,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2539</v>
+        <v>2998</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>127</v>
+        <v>149.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>-6 jours vs 06/10/2026</t>
+          <t>-2 jours vs 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2793,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>22 219 sacs</t>
+          <t>26 235 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1111.0 t</t>
+          <t>1311.7 t</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2810,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>137 781 sacs</t>
+          <t>133 765 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6889.0 t</t>
+          <t>6688.3 t</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2840,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 174 sacs</t>
+          <t>3 747 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>158.7 t</t>
+          <t>187.4 t</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2857,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>131 210 sacs</t>
+          <t>137 255 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>6560.5 t</t>
+          <t>6862.8 t</t>
         </is>
       </c>
     </row>
@@ -2974,14 +2882,14 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 29/07/2026 = 137 781 sacs (6889.0 t).</t>
+          <t>ANALYSE: Stock restant au 29/07/2026 = 133 765 sacs (6688.3 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hausse moy/jour post-stock (+9.5 t/j) — pas d'effet visible de la hausse de prix.</t>
+          <t>Hausse moy/jour post-stock (+4.4 t/j) — pas d'effet visible de la hausse de prix.</t>
         </is>
       </c>
     </row>
@@ -3002,7 +2910,7 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 17/09/2026 (43 jours de stock restant).</t>
+          <t>Date de rupture probable: 09/09/2026 (36 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3324,10 +3232,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>258.4</v>
+        <v>259.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -3495,18 +3403,18 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>239.8</v>
+        <v>241.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>3.98:1</t>
+          <t>4.01:1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="20">
@@ -3524,18 +3432,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>462.6</v>
+        <v>492.6</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>51.7</v>
+        <v>61.7</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8.95:1</t>
+          <t>7.98:1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8.949999999999999</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="21">
@@ -3553,18 +3461,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>259.7</v>
+        <v>292.2</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>57.6</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>4.51:1</t>
+          <t>5.07:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4.51</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="22">
@@ -3582,18 +3490,18 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>300.2</v>
+        <v>310.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>7.93:1</t>
+          <t>8.14:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7.93</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3637,18 +3545,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>4.28:1</t>
+          <t>4.3:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="25">
@@ -3666,18 +3574,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>284.9</v>
+        <v>299.9</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>91</v>
+        <v>97.2</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>3.13:1</t>
+          <t>3.09:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="26">
@@ -3753,18 +3661,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>121.7</v>
+        <v>139.2</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>57.6</v>
+        <v>60.8</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2.11:1</t>
+          <t>2.29:1</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="29">
@@ -3782,18 +3690,18 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>138.8</v>
+        <v>141.8</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2.71:1</t>
+          <t>2.73:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="30">
@@ -3837,18 +3745,18 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>242.1</v>
+        <v>256.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2.57:1</t>
+          <t>2.64:1</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="32">
@@ -3866,18 +3774,18 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>108.4</v>
+        <v>177.8</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>48.4</v>
+        <v>76.5</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2.24:1</t>
+          <t>2.32:1</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="33">
@@ -3895,18 +3803,18 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>13.2</v>
+        <v>109.8</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.9</v>
+        <v>45.9</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>1.67:1</t>
+          <t>2.39:1</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.67</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="37">

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 29-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 29-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 30-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 30-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Juillet" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,18 +49,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -85,14 +80,14 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -125,17 +120,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,19 +180,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -322,12 +316,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$D$5:$D$33</f>
+              <f>'T5 - Tendance Juillet'!$D$5:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$E$5:$E$33</f>
+              <f>'T5 - Tendance Juillet'!$E$5:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -469,12 +463,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$A$5:$A$33</f>
+              <f>'T5 - Tendance Juillet'!$A$5:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'T5 - Tendance Juillet'!$G$5:$G$33</f>
+              <f>'T5 - Tendance Juillet'!$G$5:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -899,7 +893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01/07 au 29/07/2026 (25j). Livree. lun-sam. Mise a jour 29/07/2026.</t>
+          <t>01/07 au 31/07/2026 (27j). Livree. lun-sam. Mise a jour 31/07/2026.</t>
         </is>
       </c>
     </row>
@@ -926,7 +920,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 28/07</t>
+          <t>Evolution vs 29/07</t>
         </is>
       </c>
     </row>
@@ -942,14 +936,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1826.2</v>
+        <v>1928.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>73</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-0.9 t/j</t>
+          <t>-1.6 t/j</t>
         </is>
       </c>
     </row>
@@ -965,14 +959,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1420.6</v>
+        <v>1520</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>+0.1 t/j</t>
+        <v>56.3</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -988,14 +982,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>775.5</v>
+        <v>832.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+0.8 t/j</t>
+        <v>30.8</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1011,14 +1005,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>541.2</v>
+        <v>567.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>-0.6 t/j</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1028,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>400.9</v>
+        <v>424.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1057,14 +1051,14 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>353.2</v>
+        <v>363.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+        <v>13.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-0.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1080,14 +1074,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>293.2</v>
+        <v>299</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>11.1</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1103,14 +1097,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>273.7</v>
+        <v>283.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+0.4 t/j</t>
+        <v>10.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1129,11 +1123,11 @@
         <v>245.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>+0.3 t/j</t>
+        <v>9.1</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-0.7 t/j</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1143,14 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>226.3</v>
+        <v>241.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>-0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1166,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>150.3</v>
+        <v>153</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>5.7</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1195,14 +1189,14 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>144.1</v>
+        <v>148.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>+0.1 t/j</t>
+        <v>5.5</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1212,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>141.1</v>
+        <v>145.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+        <v>5.4</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1241,10 +1235,10 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -1253,99 +1247,99 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>TOTAL Ouest</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Ouest</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>3002.6</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>120.1</v>
-      </c>
-      <c r="E19" s="7" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>3186</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>TOTAL Centre</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Centre</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1635.6</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>1699.1</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>TOTAL Littoral</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>2224.5</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="E21" s="7" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>2341.7</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n">
-        <v>6862.8</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>274.5</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>+1.2 t/j vs 273.4</t>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n">
+        <v>7226.9</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-6.8 t/j vs 274.5</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Moyenne/jour globale: 274.5 t/j (5490 sacs) sur 25j.</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Moyenne/jour globale: 267.7 t/j (5353 sacs) sur 27j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (28/07): 273.4 t/j (5467 sacs) sur 24j.</t>
+          <t>Precedent (29/07): 274.5 t/j (5490 sacs) sur 25j.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1375,14 +1369,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 29/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 30/07/2026 par agence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 29/07/2026.</t>
+          <t>Livree. Ratio en sacs 50kg-equivalent. Mise a jour 31/07/2026.</t>
         </is>
       </c>
     </row>
@@ -1419,138 +1413,138 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 28/07</t>
+          <t>Evolution cmdes vs 29/07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>3.2:1</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>+19 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>3.4:1</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>5.7:1</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>+7 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3.2:1</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>+3 cmdes</t>
+          <t>3.3:1</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1569,50 +1563,50 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.2:1</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-41 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>+4 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1631,50 +1625,50 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Ahala</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1683,280 +1677,264 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>+2 cmdes</t>
+          <t>2.5:1</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>3.0:1</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>-6 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>0.5:1</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.3:1</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>3.1:1</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-3 cmdes</t>
+          <t>1.9:1</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Djeleng</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>0.8:1</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>nouveau</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>2.4:1</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>-18 cmdes vs 105</t>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>-6 cmdes vs 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Distribution ratios (bundle seulement)</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Nb cmdes</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Part</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Tranche</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Nb cmdes</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Part</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= 3:1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>72%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>&lt;= 3:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>&gt; 20:1</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -1968,39 +1946,24 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>&gt; 20:1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>0%</t>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.4:1 (vs 2.2:1 le 28/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 29/07 (87 cmdes soja Livrées). Comparaison vs 28/07 (105 cmdes, extraction precedente).</t>
+          <t>Ratio global: 2.7:1 (vs 2.4:1 le 29/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 30/07 (dernier jour complet, 81 cmdes soja). Le 31/07 est une extraction matinale (149 lignes au total).</t>
         </is>
       </c>
     </row>
@@ -2015,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2032,7 +1995,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 29/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2049,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 28/07</t>
+          <t>Nouveau vs 29/07</t>
         </is>
       </c>
     </row>
@@ -2096,36 +2059,36 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126570</t>
+          <t>SO2607-126620</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2502-01255 -  SIETCHIPING</t>
+          <t>CU2605-14461 -  ETS MEKATALEO (KAMDEM TAKOUGANG LEONCE HONORE)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2137,36 +2100,36 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126410</t>
+          <t>SO2607-126631</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00160 -  PROVENDERIE LA GRACE DIVINE</t>
+          <t>CU2407-00606 -  Proal</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2178,36 +2141,36 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126546</t>
+          <t>SO2607-126702</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00159 -  SIGNE WILLIAM</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2219,36 +2182,36 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126394</t>
+          <t>SO2607-126625</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00353 -  PROVOCAM</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2260,22 +2223,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126456</t>
+          <t>SO2607-126735</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -2289,7 +2252,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2301,36 +2264,36 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126559</t>
+          <t>SO2607-126720</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2342,36 +2305,36 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126435</t>
+          <t>SO2607-126633</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2383,22 +2346,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126415</t>
+          <t>SO2607-126644</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00143 -  CLIENTS COMPTOIR BERTOUA</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -2412,7 +2375,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2424,22 +2387,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126416</t>
+          <t>SO2607-126683</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -2453,7 +2416,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2465,17 +2428,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126473</t>
+          <t>SO2607-126755</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2494,124 +2457,42 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126576</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Nkolbisson</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Centre</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>SO2607-126547</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Ndobo</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Littoral</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Livrée</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Total soja-only: 12 cmdes (9.6 t) le 29/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (28/07): 15 cmdes (6.4 t)</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Total soja-only: 10 cmdes (4.8 t) le 30/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (29/07): 12 cmdes (9.6 t)</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stock physique au 21/07/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 21/07/2026→29/07/2026 deduites du stock. Mise a jour 29/07/2026.</t>
+          <t>Stock physique au 21/07/2026: 160 000 sacs (8000 t). Methode corrigee: ventes post-stock 21/07/2026→31/07/2026 deduites du stock. Mise a jour 31/07/2026.</t>
         </is>
       </c>
     </row>
@@ -2690,22 +2571,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3748</v>
+        <v>3501</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>187.4</v>
+        <v>175.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>-2 jours vs 10/09/2026</t>
+          <t>+1 jours vs 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2716,22 +2597,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4497</v>
+        <v>4202</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>224.9</v>
+        <v>210.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>-1 jours vs 02/09/2026</t>
+          <t>+1 jours vs 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2742,27 +2623,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2998</v>
+        <v>2801</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>149.9</v>
+        <v>140.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>-2 jours vs 21/09/2026</t>
+          <t>+1 jours vs 19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2788,34 +2669,34 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Ventes post-stock 22→29/07</t>
+          <t>Ventes post-stock 22→31/07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>26 235 sacs</t>
+          <t>31 512 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1311.7 t</t>
+          <t>1575.6 t</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Stock restant au 29/07</t>
+          <t>Stock restant au 31/07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>133 765 sacs</t>
+          <t>128 488 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6688.3 t</t>
+          <t>6424.4 t</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2708,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7 j (lun-sam)</t>
+          <t>9 j (lun-sam)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -2840,12 +2721,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 747 sacs</t>
+          <t>3 501 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>187.4 t</t>
+          <t>175.1 t</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2738,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>137 255 sacs</t>
+          <t>144 537 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>6862.8 t</t>
+          <t>7226.9 t</t>
         </is>
       </c>
     </row>
@@ -2880,37 +2761,37 @@
       <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ANALYSE: Stock restant au 29/07/2026 = 133 765 sacs (6688.3 t).</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ANALYSE: Stock restant au 31/07/2026 = 128 488 sacs (6424.4 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hausse moy/jour post-stock (+4.4 t/j) — pas d'effet visible de la hausse de prix.</t>
+          <t>Baisse moy/jour post-stock (-12.3 t/j) — effet possible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Seules les ventes 22→29/07 (post-stock) sont deduites du stock pour calculer le stock restant au 29/07.</t>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Seules les ventes 22→31/07 (post-stock) sont deduites du stock pour calculer le stock restant au 31/07.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 09/09/2026 (36 jours de stock restant).</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 12/09/2026 (37 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2947,7 +2828,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Données Livrées au 29/07/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
+          <t>Données Livrées au 31/07/2026. Jours ouvrés (lun-sam) en couleur, dimanches en gris.</t>
         </is>
       </c>
     </row>
@@ -3105,26 +2986,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3305,26 +3186,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3345,18 +3226,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>345.3</v>
+        <v>360.3</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>75.5</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>4.57:1</t>
+          <t>4.77:1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4.57</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="18">
@@ -3432,18 +3313,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>492.6</v>
+        <v>542.6</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>61.7</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>7.98:1</t>
+          <t>8.79:1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7.98</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3461,18 +3342,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>292.2</v>
+        <v>312</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>57.6</v>
+        <v>60</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>5.07:1</t>
+          <t>5.2:1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5.07</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="22">
@@ -3505,26 +3386,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3545,18 +3426,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>425</v>
+        <v>438.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>4.3:1</t>
+          <t>4.38:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="25">
@@ -3574,18 +3455,18 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>299.9</v>
+        <v>301.9</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>97.2</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>3.09:1</t>
+          <t>3.11:1</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="26">
@@ -3603,47 +3484,47 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>278.9</v>
+        <v>306.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>93</v>
+        <v>103.5</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
+          <t>2.97:1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D27" s="18" t="n">
-        <v>207.9</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>2.77:1</t>
+      <c r="D27" s="17" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -3661,18 +3542,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>139.2</v>
+        <v>155.9</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>60.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2.29:1</t>
+          <t>2.35:1</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="29">
@@ -3690,10 +3571,10 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>141.8</v>
+        <v>143.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -3705,26 +3586,26 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3745,10 +3626,10 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>256.3</v>
+        <v>264.8</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>100.4</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -3774,18 +3655,18 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>177.8</v>
+        <v>196.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>76.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2.32:1</t>
+          <t>2.37:1</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="33">
@@ -3803,57 +3684,115 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>109.8</v>
+        <v>154.6</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>45.9</v>
+        <v>60.9</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2.39:1</t>
+          <t>2.54:1</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Jeu</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>2.74:1</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Ven</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>2.49:1</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début juillet) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 - Moy jour soja par agence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 30-07" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 30-07" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 - Commandes soja 31-07" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 - Soja-only 31-07" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 - Stock soja et rupture" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5 - Tendance Juillet" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,7 +45,8 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <i val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +56,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -83,11 +84,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,17 +116,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,20 +174,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -920,7 +916,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Evolution vs 29/07</t>
+          <t>Evolution vs 31/07 matinale</t>
         </is>
       </c>
     </row>
@@ -936,14 +932,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1928.2</v>
+        <v>1984.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>-1.6 t/j</t>
+          <t>+2.1 t/j</t>
         </is>
       </c>
     </row>
@@ -959,14 +955,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1520</v>
+        <v>1548.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>56.3</v>
+        <v>57.4</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>+1.1 t/j</t>
         </is>
       </c>
     </row>
@@ -982,14 +978,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>832.9</v>
+        <v>856.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>30.8</v>
+        <v>31.7</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>-0.2 t/j</t>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
@@ -1005,14 +1001,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>567.8</v>
+        <v>601</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-0.6 t/j</t>
+          <t>+1.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1028,14 +1024,14 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>424.9</v>
+        <v>439.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.7</v>
+        <v>16.3</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+0.5 t/j</t>
         </is>
       </c>
     </row>
@@ -1051,60 +1047,60 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>363.2</v>
+        <v>371.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-0.7 t/j</t>
+          <t>+0.3 t/j</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>299</v>
+        <v>326.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11.1</v>
+        <v>12.1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-0.7 t/j</t>
+          <t>+1.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>283.3</v>
+        <v>303.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-0.5 t/j</t>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
@@ -1120,14 +1116,14 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>245.1</v>
+        <v>271</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>-0.7 t/j</t>
+          <t>+1.0 t/j</t>
         </is>
       </c>
     </row>
@@ -1143,44 +1139,44 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>241.6</v>
+        <v>246.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>+0.2 t/j</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>153</v>
+        <v>172.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+0.9 t/j</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1189,37 +1185,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>148.3</v>
+        <v>160.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-0.3 t/j</t>
+          <t>+0.6 t/j</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>145.1</v>
+        <v>153.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>-0.3 t/j</t>
+        <v>5.7</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1235,14 +1231,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>-0.1 t/j</t>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1254,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>3186</v>
+        <v>3280.5</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>118</v>
+        <v>121.5</v>
       </c>
       <c r="E19" s="6" t="n"/>
     </row>
@@ -1277,10 +1273,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1699.1</v>
+        <v>1753.1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>62.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E20" s="6" t="n"/>
     </row>
@@ -1296,10 +1292,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2341.7</v>
+        <v>2478.7</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>86.7</v>
+        <v>91.8</v>
       </c>
       <c r="E21" s="6" t="n"/>
     </row>
@@ -1311,14 +1307,14 @@
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>7226.9</v>
+        <v>7512.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>267.7</v>
+        <v>278.2</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-6.8 t/j vs 274.5</t>
+          <t>+10.6 t/j vs 267.7</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1328,14 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 267.7 t/j (5353 sacs) sur 27j.</t>
+          <t>Moyenne/jour globale: 278.2 t/j (5564 sacs) sur 27j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (29/07): 274.5 t/j (5490 sacs) sur 25j.</t>
+          <t>Precedent (31/07 matinale): 267.7 t/j (5353 sacs) sur 27j.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1365,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 2 - Commandes SOJA le 30/07/2026 par agence</t>
+          <t>TABLEAU 2 - Commandes SOJA le 31/07/2026 par agence</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1409,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Evolution cmdes vs 29/07</t>
+          <t>Evolution cmdes vs 30/07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1429,13 +1425,13 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1444,95 +1440,95 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>+19 cmdes</t>
+          <t>+13 cmdes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Messassi</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3.4:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>+9 cmdes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Famla</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1.5:1</t>
+          <t>3.3:1</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>+1 cmdes</t>
+          <t>+8 cmdes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Mbouda</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>3.3:1</t>
+          <t>2.5:1</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1544,69 +1540,69 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mbouda</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
+          <t>2.6:1</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>+2 cmdes</t>
+          <t>+5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.4:1</t>
+          <t>2.7:1</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>-5 cmdes</t>
+          <t>-14 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Messassi</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1615,22 +1611,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>-7 cmdes</t>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
@@ -1646,60 +1642,60 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>2.8:1</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ahala</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2.5:1</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1708,60 +1704,60 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>-6 cmdes</t>
+          <t>2.1:1</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>+4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0.5:1</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1770,34 +1766,34 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2.3:1</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>-4 cmdes</t>
+          <t>1.1:1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>nouveau</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkoabang</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -1811,130 +1807,146 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>1.9:1</t>
+          <t>2.4:1</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>-2 cmdes</t>
+          <t>-5 cmdes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ahala</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>2.2:1</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>-3 cmdes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>-6 cmdes vs 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>2.6:1</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>+28 cmdes vs 81</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tranche</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Nb cmdes</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Part</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>&lt;= 3:1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>72%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3-5:1</t>
+          <t>&lt;= 3:1</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>64%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>5-10:1</t>
+          <t>3-5:1</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>10-20:1</t>
+          <t>5-10:1</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>&gt; 20:1</t>
+          <t>10-20:1</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -1946,24 +1958,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 20:1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>NOTE: Le prix du soja a augmente de +2 000 XAF/sac le 23/07/2026 (effet plein visible a partir de ce jour).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Ratio global: 2.7:1 (vs 2.4:1 le 29/07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Note: T2/T3 portent sur le 30/07 (dernier jour complet, 81 cmdes soja). Le 31/07 est une extraction matinale (149 lignes au total).</t>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Ratio global: 2.6:1 (vs 2.7:1 le 30/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Note: T2/T3 portent sur le 31/07 (dernier jour du mois, 109 cmdes soja Livrées). Comparaison vs 30/07 (extraction precedente matinale qui n'avait pas le 31/07 complet).</t>
         </is>
       </c>
     </row>
@@ -1978,7 +2005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1995,7 +2022,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU 3 - SOJA sans concentres le 30/07/2026</t>
+          <t>TABLEAU 3 - SOJA sans concentres le 31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2076,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Nouveau vs 29/07</t>
+          <t>Nouveau vs 30/07</t>
         </is>
       </c>
     </row>
@@ -2059,17 +2086,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126620</t>
+          <t>SO2607-126949</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CU2605-14461 -  ETS MEKATALEO (KAMDEM TAKOUGANG LEONCE HONORE)</t>
+          <t>CU2407-00722 -  KUE FOTSO ARNAULO</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Famla</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2088,7 +2115,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2100,17 +2127,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126631</t>
+          <t>SO2607-126917</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00606 -  Proal</t>
+          <t>CU2409-01111 -  KOUAM TALLA JEAN STEPHANE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2129,7 +2156,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2141,36 +2168,36 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126702</t>
+          <t>SO2607-126884</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2182,36 +2209,36 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126625</t>
+          <t>SO2607-126845</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2223,36 +2250,36 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126735</t>
+          <t>SO2607-126850</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2264,22 +2291,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126720</t>
+          <t>SO2607-126946</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00149 -  CLIENTS COMPTOIR NKOLBISSON</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -2293,7 +2320,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2305,36 +2332,36 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126633</t>
+          <t>SO2607-126992</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00148 -  CLIENTS COMPTOIR NKOABANG</t>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Nkoabang</t>
+          <t>Ndobo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2346,36 +2373,36 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126644</t>
+          <t>SO2607-126999</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2407-00147 -  CLIENTS COMPTOIR NGAOUNDERE</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2387,7 +2414,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126683</t>
+          <t>SO2607-126847</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2416,7 +2443,7 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -2428,17 +2455,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126755</t>
+          <t>SO2607-126875</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2457,42 +2484,165 @@
           <t>Livrée</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126825</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126892</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Ngaoundere</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Centre</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126844</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Ndobo</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Total soja-only: 10 cmdes (4.8 t) le 30/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (29/07): 12 cmdes (9.6 t)</t>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Total soja-only: 13 cmdes (3.8 t) le 31/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (30/07): 10 cmdes (4.8 t)</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2721,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3501</v>
+        <v>4016</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>175.1</v>
+        <v>200.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>+1 jours vs 09/09/2026</t>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>-6 jours vs 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -2597,22 +2747,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4202</v>
+        <v>4819</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>210.1</v>
+        <v>240.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>+1 jours vs 02/09/2026</t>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>-5 jours vs 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2623,27 +2773,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2801</v>
+        <v>3213</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>140.1</v>
+        <v>160.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>+1 jours vs 19/09/2026</t>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-7 jours vs 23/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2674,12 +2824,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>31 512 sacs</t>
+          <t>36 141 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1575.6 t</t>
+          <t>1807.1 t</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2841,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>128 488 sacs</t>
+          <t>123 859 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6424.4 t</t>
+          <t>6192.9 t</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2871,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3 501 sacs</t>
+          <t>4 015 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>175.1 t</t>
+          <t>200.8 t</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2888,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>144 537 sacs</t>
+          <t>150 245 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>7226.9 t</t>
+          <t>7512.2 t</t>
         </is>
       </c>
     </row>
@@ -2763,26 +2913,26 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 31/07/2026 = 128 488 sacs (6424.4 t).</t>
+          <t>ANALYSE: Stock restant au 31/07/2026 = 123 859 sacs (6192.9 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Baisse moy/jour post-stock (-12.3 t/j) — effet possible de la hausse de prix.</t>
+          <t>Hausse moy/jour post-stock (+25.7 t/j) — pas d'effet visible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Seules les ventes 22→31/07 (post-stock) sont deduites du stock pour calculer le stock restant au 31/07.</t>
         </is>
@@ -2791,7 +2941,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Date de rupture probable: 12/09/2026 (37 jours de stock restant).</t>
+          <t>Date de rupture probable: 05/09/2026 (31 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3055,18 +3205,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>321.6</v>
+        <v>322.6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60.8</v>
+        <v>61.8</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>5.29:1</t>
+          <t>5.22:1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="12">
@@ -3255,18 +3405,18 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>290.3</v>
+        <v>295.3</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>73.5</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>3.95:1</t>
+          <t>4.02:1</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="19">
@@ -3313,18 +3463,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>542.6</v>
+        <v>568.6</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>61.7</v>
+        <v>63.5</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8.79:1</t>
+          <t>8.96:1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8.789999999999999</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3371,18 +3521,18 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>310.2</v>
+        <v>332</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>38.1</v>
+        <v>39.6</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>8.14:1</t>
+          <t>8.38:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3513,18 +3663,18 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>218.9</v>
+        <v>232.8</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>78.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>2.8:1</t>
+          <t>2.82:1</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="28">
@@ -3571,18 +3721,18 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>143.5</v>
+        <v>151</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>52.5</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2.73:1</t>
+          <t>2.88:1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="30">
@@ -3655,18 +3805,18 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>196.7</v>
+        <v>202.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2.37:1</t>
+          <t>2.38:1</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="33">
@@ -3684,18 +3834,18 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>154.6</v>
+        <v>166.7</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>60.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2.54:1</t>
+          <t>2.57:1</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="34">
@@ -3713,18 +3863,18 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>120.7</v>
+        <v>165.4</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>44.1</v>
+        <v>62.5</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2.74:1</t>
+          <t>2.65:1</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="35">
@@ -3742,22 +3892,22 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>13.6</v>
+        <v>160.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.5</v>
+        <v>63.1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2.49:1</t>
+          <t>2.55:1</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>

--- a/download/analyse_soja_juillet.xlsx
+++ b/download/analyse_soja_juillet.xlsx
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +181,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -937,9 +936,9 @@
       <c r="D5" s="4" t="n">
         <v>73.5</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>+2.1 t/j</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -955,14 +954,14 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1548.5</v>
+        <v>1564.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>57.4</v>
+        <v>57.9</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>+1.1 t/j</t>
+          <t>+0.6 t/j</t>
         </is>
       </c>
     </row>
@@ -983,9 +982,9 @@
       <c r="D7" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1001,14 +1000,14 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>601</v>
+        <v>608.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>+1.2 t/j</t>
+          <t>+0.3 t/j</t>
         </is>
       </c>
     </row>
@@ -1029,9 +1028,9 @@
       <c r="D9" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>+0.5 t/j</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1052,9 +1051,9 @@
       <c r="D10" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>+0.3 t/j</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1075,9 +1074,9 @@
       <c r="D11" s="4" t="n">
         <v>12.1</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>+1.6 t/j</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1092,14 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>303.3</v>
+        <v>303.7</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1116,10 +1115,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>271</v>
+        <v>297.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -1144,9 +1143,9 @@
       <c r="D14" s="4" t="n">
         <v>9.1</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>+0.2 t/j</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1161,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>172.3</v>
+        <v>172.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>6.4</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>+0.9 t/j</t>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1190,9 +1189,9 @@
       <c r="D16" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>+0.6 t/j</t>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1208,14 +1207,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>153.5</v>
+        <v>156.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>stable</t>
+        <v>5.8</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+0.1 t/j</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>+0.1 t/j</t>
+          <t>stable</t>
         </is>
       </c>
     </row>
@@ -1273,10 +1272,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1753.1</v>
+        <v>1764.2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>64.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="E20" s="6" t="n"/>
     </row>
@@ -1292,10 +1291,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2478.7</v>
+        <v>2521.2</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E21" s="6" t="n"/>
     </row>
@@ -1307,14 +1306,14 @@
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>7512.2</v>
+        <v>7565.9</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>278.2</v>
+        <v>280.2</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>+10.6 t/j vs 267.7</t>
+          <t>+2.0 t/j vs 278.2</t>
         </is>
       </c>
     </row>
@@ -1328,14 +1327,14 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Moyenne/jour globale: 278.2 t/j (5564 sacs) sur 27j.</t>
+          <t>Moyenne/jour globale: 280.2 t/j (5604 sacs) sur 27j.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Precedent (31/07 matinale): 267.7 t/j (5353 sacs) sur 27j.</t>
+          <t>Precedent (31/07 matinale): 278.2 t/j (5564 sacs) sur 27j.</t>
         </is>
       </c>
     </row>
@@ -1456,17 +1455,17 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
+          <t>2.8:1</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1487,22 +1486,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3.3:1</t>
+          <t>3.2:1</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>+8 cmdes</t>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
@@ -1549,91 +1548,91 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2.6:1</t>
+          <t>2.9:1</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>+5 cmdes</t>
+          <t>+7 cmdes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2.7:1</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>-14 cmdes</t>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Bertoua</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3.0:1</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>+1 cmdes</t>
+          <t>2.7:1</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-16 cmdes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nkolbisson</t>
+          <t>Bertoua</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1642,17 +1641,17 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2.8:1</t>
+          <t>3.0:1</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1664,38 +1663,38 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Nkolbisson</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.5:1</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>-2 cmdes</t>
+          <t>2.8:1</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>+1 cmdes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nkongsamba</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1714,19 +1713,19 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2.1:1</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>+4 cmdes</t>
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>-4 cmdes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Buea</t>
+          <t>Nkongsamba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1735,29 +1734,29 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2.9:1</t>
+          <t>2.1:1</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>+3 cmdes</t>
+          <t>+2 cmdes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Buea</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1766,22 +1765,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1.1:1</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>nouveau</t>
+          <t>2.9:1</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>+3 cmdes</t>
         </is>
       </c>
     </row>
@@ -1855,13 +1854,13 @@
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1870,12 +1869,12 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>+28 cmdes vs 81</t>
+          <t>+20 cmdes vs 99</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Distribution ratios (bundle seulement)</t>
         </is>
@@ -1905,11 +1904,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -1920,11 +1919,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1982,12 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Ratio global: 2.6:1 (vs 2.7:1 le 30/07).</t>
+          <t>Ratio global: 2.6:1 (vs 2.6:1 le 30/07).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Note: T2/T3 portent sur le 31/07 (dernier jour du mois, 109 cmdes soja Livrées). Comparaison vs 30/07 (extraction precedente matinale qui n'avait pas le 31/07 complet).</t>
         </is>
@@ -2005,7 +2004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2414,29 +2413,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126847</t>
+          <t>SO2607-127005</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
+          <t>CU2406-00004 -  CLIENT COMPTOIR AXE LOURD</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Djeleng</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -2455,22 +2454,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126875</t>
+          <t>SO2607-126847</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
+          <t>CU2407-00140 -  CLIENTS COMPTOIR BAF-DJELENG</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Pk11</t>
+          <t>Djeleng</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2496,29 +2495,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126825</t>
+          <t>SO2607-126875</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CU2504-01319 -  ONANA JUSTIN</t>
+          <t>CU2406-00012 -  CLIENTS COMPTOIR PK11</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Ngaoundere</t>
+          <t>Pk11</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Littoral</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -2537,7 +2536,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126892</t>
+          <t>SO2607-126825</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2578,22 +2577,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SO2607-126844</t>
+          <t>SO2607-126892</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+          <t>CU2504-01319 -  ONANA JUSTIN</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ndobo</t>
+          <t>Ngaoundere</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Littoral</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -2614,35 +2613,76 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SO2607-126844</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>CU2407-00139 -  CLIENT COMPTOIR SIEGE ZSCL00114 (CLIENT COMPTOIR SIEGE)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Ndobo</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Littoral</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Livrée</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Total soja-only: 13 cmdes (3.8 t) le 31/07/2026</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Precedent (30/07): 10 cmdes (4.8 t)</t>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Total soja-only: 14 cmdes (3.9 t) le 31/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Precedent (30/07): 14 cmdes (5.2 t)</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2761,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4016</v>
+        <v>4063</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>200.8</v>
+        <v>203.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>-6 jours vs 12/09/2026</t>
+          <t>-1 jours vs 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2747,22 +2787,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4819</v>
+        <v>4876</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>240.9</v>
+        <v>243.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>-5 jours vs 05/09/2026</t>
+          <t>-1 jours vs 31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2773,27 +2813,27 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3213</v>
+        <v>3251</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>160.6</v>
+        <v>162.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>-7 jours vs 23/09/2026</t>
+          <t>-1 jours vs 15/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Parametres</t>
         </is>
@@ -2824,12 +2864,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>36 141 sacs</t>
+          <t>36 569 sacs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1807.1 t</t>
+          <t>1828.5 t</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2881,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>123 859 sacs</t>
+          <t>123 431 sacs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6192.9 t</t>
+          <t>6171.5 t</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2911,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>4 015 sacs</t>
+          <t>4 063 sacs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>200.8 t</t>
+          <t>203.2 t</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2928,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>150 245 sacs</t>
+          <t>151 319 sacs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>7512.2 t</t>
+          <t>7565.9 t</t>
         </is>
       </c>
     </row>
@@ -2913,35 +2953,35 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ANALYSE: Stock restant au 31/07/2026 = 123 859 sacs (6192.9 t).</t>
+          <t>ANALYSE: Stock restant au 31/07/2026 = 123 431 sacs (6171.5 t).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hausse moy/jour post-stock (+25.7 t/j) — pas d'effet visible de la hausse de prix.</t>
+          <t>Hausse moy/jour post-stock (+2.4 t/j) — pas d'effet visible de la hausse de prix.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Methode corrigee: le stock de 160 000 sacs est mesure au 21/07. Les ventes 01→21/07 sont deja consommees.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Seules les ventes 22→31/07 (post-stock) sont deduites du stock pour calculer le stock restant au 31/07.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Date de rupture probable: 05/09/2026 (31 jours de stock restant).</t>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Date de rupture probable: 04/09/2026 (30 jours de stock restant).</t>
         </is>
       </c>
     </row>
@@ -3136,26 +3176,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3292,18 +3332,18 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>240.8</v>
+        <v>261.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>55.6</v>
+        <v>63.8</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>4.33:1</t>
+          <t>4.1:1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
@@ -3336,26 +3376,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3521,41 +3561,41 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>332</v>
+        <v>340.4</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>39.6</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>8.38:1</t>
+          <t>8.59:1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3576,18 +3616,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>438.5</v>
+        <v>441.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>100</v>
+        <v>101.4</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>4.38:1</t>
+          <t>4.35:1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="25">
@@ -3649,26 +3689,26 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="16" t="n">
         <v>232.8</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="16" t="n">
         <v>82.7</v>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>2.82:1</t>
         </is>
@@ -3736,26 +3776,26 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Dim</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3834,18 +3874,18 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>166.7</v>
+        <v>168.4</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2.57:1</t>
+          <t>2.58:1</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="34">
@@ -3863,10 +3903,10 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>165.4</v>
+        <v>166.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -3892,57 +3932,57 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>160.9</v>
+        <v>179.2</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>63.1</v>
+        <v>68.8</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2.55:1</t>
+          <t>2.61:1</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>NOTES DE LECTURE:</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Soja" (bleu) montre la consommation journalière de tourteaux de soja — impactée par la hausse +1 000 FCFA/sac (début juillet) puis +2 000 FCFA/sac (23/07).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>• La ligne "Concentrés" (or) montre la consommation journalière de concentrés (BELGO Chair/Ponte/Porc).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>• Le ratio soja:conc cible est 3:1 (objectif bundle). Un ratio supérieur signifie que les clients achètent plus de soja que de concentrés — dégradation du bundle.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>• Les dimanches sont grisés (pas de ventes). Le 23/07 est surligné en rouge (date de la 2e hausse tarifaire +2 000 FCFA/sac).</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>• À observer: la tendance soja après le 23/07 vs avant — l'effet prix devrait ralentir la consommation soja si les clients sont sensibles au prix.</t>
         </is>
